--- a/trip_account.xlsx
+++ b/trip_account.xlsx
@@ -163,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -194,6 +194,12 @@
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -203,11 +209,14 @@
     <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -588,7 +597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -611,7 +620,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间：2026-07-31 14:30   |   汇率：1 元 ≈ 21 日元（近似汇率，可在网页中实时调整）</t>
+          <t>更新时间：2026-08-01 11:47   |   汇率：1 元 ≈ 21 日元（近似汇率，可在网页中实时调整）</t>
         </is>
       </c>
     </row>
@@ -766,23 +775,59 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr"/>
-      <c r="B8" s="12" t="inlineStr"/>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>张</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>换汇 RMB→日元（平分）</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>AA分摊</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="11" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr"/>
+      <c r="B9" s="14" t="inlineStr"/>
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr"/>
-      <c r="E8" s="14" t="n">
+      <c r="D9" s="14" t="inlineStr"/>
+      <c r="E9" s="16" t="n">
+        <v>3995.62</v>
+      </c>
+      <c r="F9" s="14" t="inlineStr"/>
+      <c r="G9" s="16" t="n">
         <v>1995.62</v>
       </c>
-      <c r="F8" s="12" t="inlineStr"/>
-      <c r="G8" s="14" t="n">
-        <v>1995.62</v>
-      </c>
-      <c r="H8" s="14" t="n">
-        <v>0</v>
+      <c r="H9" s="16" t="n">
+        <v>2000</v>
       </c>
     </row>
   </sheetData>
@@ -800,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -847,41 +892,41 @@
         <v>1995.62</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>1995.62</v>
-      </c>
-      <c r="D4" s="15" t="n">
-        <v>0</v>
+        <v>2995.62</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>-1000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>张</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="15" t="n">
-        <v>0</v>
+        <v>1000</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>1000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>总计</t>
         </is>
       </c>
-      <c r="B6" s="18" t="n">
-        <v>1995.62</v>
-      </c>
-      <c r="C6" s="19" t="inlineStr"/>
+      <c r="B6" s="21" t="n">
+        <v>3995.62</v>
+      </c>
+      <c r="C6" s="22" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>类别支出构成</t>
         </is>
@@ -907,40 +952,53 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>交通</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>1134</v>
-      </c>
-      <c r="C11" s="21" t="n">
-        <v>0.5682444553572323</v>
+        <v>2000</v>
+      </c>
+      <c r="C11" s="24" t="n">
+        <v>0.5005481001696859</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>签证</t>
+          <t>交通</t>
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>859.3200000000001</v>
-      </c>
-      <c r="C12" s="21" t="n">
-        <v>0.4306030206151472</v>
+        <v>1134</v>
+      </c>
+      <c r="C12" s="24" t="n">
+        <v>0.2838107727962119</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t>签证</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>859.3200000000001</v>
+      </c>
+      <c r="C13" s="24" t="n">
+        <v>0.2150654967189072</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
           <t>购物</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n">
+      <c r="B14" s="7" t="n">
         <v>2.3</v>
       </c>
-      <c r="C13" s="21" t="n">
-        <v>0.001152524027620489</v>
+      <c r="C14" s="24" t="n">
+        <v>0.0005756303151951387</v>
       </c>
     </row>
   </sheetData>
@@ -974,59 +1032,65 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="inlineStr">
-        <is>
-          <t>✅ 已平账，双方无需结算。</t>
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>姜 需向 张 支付，以结清 AA 差额。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>付款人</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr"/>
-      <c r="C5" s="23" t="n"/>
-      <c r="D5" s="24" t="n"/>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>姜</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="27" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>收款人</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr"/>
-      <c r="C6" s="23" t="n"/>
-      <c r="D6" s="24" t="n"/>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>张</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="n"/>
+      <c r="D6" s="27" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>结算金额(元)</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="n"/>
-      <c r="D7" s="24" t="n"/>
+      <c r="B7" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C7" s="26" t="n"/>
+      <c r="D7" s="27" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>结算金额(日元)</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C8" s="23" t="n"/>
-      <c r="D8" s="24" t="n"/>
+          <t>¥21,000</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="n"/>
+      <c r="D8" s="27" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
